--- a/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
@@ -37,7 +37,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,9 +91,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -528,7 +520,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, SHETTY</t>
         </is>
@@ -548,7 +540,7 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -578,7 +570,7 @@
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, MATSUOKA</t>
         </is>
@@ -598,7 +590,7 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -628,7 +620,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, SHETTY</t>
         </is>
@@ -640,42 +632,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SHETTY  (24H)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>KOPP VANUZZI</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -700,7 +692,7 @@
           <t>SHETTY, PATEL</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -725,7 +717,7 @@
           <t>MATSUOKA, SHETTY</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -750,7 +742,7 @@
           <t>MATSUOKA, PATEL</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -775,7 +767,7 @@
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -800,49 +792,49 @@
           <t>SHETTY, PATEL</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>PATEL</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>MATSUOKA</t>
         </is>
@@ -857,7 +849,7 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -887,7 +879,7 @@
           <t>BUTT</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, PATEL</t>
         </is>
@@ -912,7 +904,7 @@
           <t>PATEL</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, BUTT</t>
         </is>
@@ -962,7 +954,7 @@
           <t>PATEL</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, BUTT</t>
         </is>
@@ -974,12 +966,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -987,7 +979,7 @@
           <t>KENNEDY</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>KENNEDY  (24H)</t>
@@ -995,21 +987,21 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PATEL</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>BUTT</t>
         </is>
@@ -1029,7 +1021,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, ALMADHOOB</t>
         </is>
@@ -1054,7 +1046,7 @@
           <t>ALMADHOOB</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, MATSUOKA</t>
         </is>
@@ -1074,7 +1066,7 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -1104,7 +1096,7 @@
           <t>ALMADHOOB</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -1124,7 +1116,7 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -1141,42 +1133,42 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>MATSUOKA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>BUTT</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>ALMADHOOB</t>
         </is>
@@ -1191,7 +1183,7 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -1221,7 +1213,7 @@
           <t>RIVERA</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, MATSUOKA</t>
         </is>
@@ -1246,7 +1238,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, RIVERA</t>
         </is>
@@ -1258,19 +1250,19 @@
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1301,7 +1293,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1344,7 +1336,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1387,7 +1379,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1430,7 +1422,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY D, SHETTY K</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -542,17 +542,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SHETTY</t>
+          <t>MATSUOKA K, SHETTY K</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KENNEDY D, MATSUOKA K</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -592,17 +592,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY D, SHETTY K</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -642,13 +642,13 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>SHETTY  (24H)</t>
+          <t>SHETTY K  (24H)</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>SHETTY, PATEL</t>
+          <t>SHETTY K, PATEL T</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SHETTY</t>
+          <t>MATSUOKA K, SHETTY K</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -734,17 +734,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>MATSUOKA K, PATEL T</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -759,17 +759,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>SHETTY, PATEL</t>
+          <t>SHETTY K, PATEL T</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>PATEL  (24H)</t>
+          <t>PATEL T  (24H)</t>
         </is>
       </c>
     </row>
@@ -830,13 +830,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT A, PATEL T</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>KENNEDY D, PATEL T</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>KENNEDY D, BUTT A</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>KENNEDY D, BUTT A</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -976,13 +976,13 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>KENNEDY D  (24H)</t>
         </is>
       </c>
     </row>
@@ -997,13 +997,13 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, ALMADHOOB</t>
+          <t>KENNEDY D, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -1043,17 +1043,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KENNEDY D, MATSUOKA K</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, ALMADHOOB</t>
+          <t>MATSUOKA K, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, ALMADHOOB</t>
+          <t>MATSUOKA K, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -1143,13 +1143,13 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA  (24H)</t>
+          <t>MATSUOKA K  (24H)</t>
         </is>
       </c>
     </row>
@@ -1164,13 +1164,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -1185,17 +1185,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, RIVERA</t>
+          <t>MATSUOKA K, RIVERA A</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KENNEDY D, MATSUOKA K</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -1235,17 +1235,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, RIVERA</t>
+          <t>KENNEDY D, RIVERA A</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -78,23 +79,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,19 +519,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -540,19 +544,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -565,19 +569,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, SHETTY</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -590,19 +594,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -615,61 +619,61 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K  (24H)</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -682,19 +686,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K, PATEL T</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, PATEL</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -707,19 +711,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, PATEL</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -732,19 +736,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, PATEL T</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -757,19 +761,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -782,61 +786,61 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K, PATEL T</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, PATEL</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>PATEL T  (24H)</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -849,19 +853,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A, PATEL T</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>PATEL, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -874,19 +878,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, PATEL T</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -899,19 +903,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, BUTT A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, PATEL</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -924,19 +928,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -949,61 +953,61 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, BUTT A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D  (24H)</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>MATSUOKA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1020,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1045,19 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, BUTT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1070,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1091,19 +1095,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1116,61 +1120,61 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, BUTT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA K  (24H)</t>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BUTT  (24H)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -1183,19 +1187,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -1208,19 +1212,19 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -1233,36 +1237,36 @@
       <c r="B33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, RIVERA</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1293,7 +1297,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1336,7 +1340,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1379,7 +1383,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1422,7 +1426,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
@@ -526,12 +526,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>SHETTY, KENNEDY</t>
+          <t>SHETTY, MATSUOKA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, KENNEDY</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, KENNEDY</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -646,13 +646,13 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>MATSUOKA  (24H)</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>MATSUOKA, PATEL</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, KENNEDY</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>MATSUOKA</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -834,13 +834,13 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>PATEL, MATSUOKA</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BUTT, MATSUOKA</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, PATEL</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>MATSUOKA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>BUTT, PATEL</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BUTT, MATSUOKA</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -980,13 +980,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA  (24H)</t>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, BUTT</t>
+          <t>KENNEDY, BUTT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>MATSUOKA, BUTT</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>MATSUOKA, KENNEDY</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>MATSUOKA, BUTT</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1168,13 +1168,13 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>RIVERA, KENNEDY</t>
+          <t>RIVERA, MATSUOKA</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, KENNEDY</t>
+          <t>ALMADHOOB, MATSUOKA</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dean Kennedy</t>
+          <t>Kazune Matsuoka</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazune Matsuoka</t>
+          <t>Dean Kennedy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
@@ -521,17 +521,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY, MATSUOKA</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, SHETTY</t>
+          <t>KENNEDY, SHETTY</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
@@ -688,12 +688,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>MATSUOKA, KENNEDY</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>PATEL, MATSUOKA</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -813,13 +813,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>PATEL  (24H)</t>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>PATEL, KENNEDY</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BUTT, KENNEDY</t>
+          <t>BUTT, PATEL</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BUTT, KENNEDY</t>
+          <t>BUTT, PATEL</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -980,13 +980,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>ALMADHOOB, BUTT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1047,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, KENNEDY</t>
+          <t>MATSUOKA, ALMADHOOB</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA, MATSUOKA</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, RIVERA</t>
+          <t>KENNEDY, RIVERA</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_March_2027.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KOPP VANUZZI, SHETTY</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
@@ -688,12 +688,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, KENNEDY</t>
+          <t>MATSUOKA, PATEL</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>PATEL, KENNEDY</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>PATEL, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>PATEL, KENNEDY</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -813,13 +813,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>BUTT, KENNEDY</t>
+          <t>BUTT, PATEL</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -980,13 +980,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>PATEL  (24H)</t>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, BUTT</t>
+          <t>KENNEDY, BUTT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1047,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, ALMADHOOB</t>
+          <t>MATSUOKA, KENNEDY</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>ALMADHOOB, MATSUOKA</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, RIVERA</t>
+          <t>ALMADHOOB, RIVERA</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
